--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>96323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>96323</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B14" t="n">
-        <v>96216</v>
+        <v>97348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R14" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B15" t="n">
-        <v>97348</v>
+        <v>96216</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R15" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,11 +2042,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>97348</v>
+        <v>96216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>96216</v>
+        <v>97348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R15" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,6 +2037,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607425</v>
+        <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>96323</v>
+        <v>97348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516155</v>
+        <v>516156</v>
       </c>
       <c r="R3" t="n">
-        <v>6348485</v>
+        <v>6348543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607424</v>
+        <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>97348</v>
+        <v>96323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516156</v>
+        <v>516155</v>
       </c>
       <c r="R4" t="n">
-        <v>6348543</v>
+        <v>6348485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1364,45 +1364,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B9" t="n">
-        <v>92206</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R9" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,50 +1466,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>92206</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R10" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>97348</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>97377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R5" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>82995</v>
+        <v>83022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129607416</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>129607418</v>
       </c>
       <c r="B10" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>82997</v>
+        <v>83024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>82995</v>
+        <v>83022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B14" t="n">
-        <v>96216</v>
+        <v>97377</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R14" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B15" t="n">
-        <v>97348</v>
+        <v>96245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R15" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,11 +2042,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>96352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607425</v>
+        <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>96352</v>
+        <v>97377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516155</v>
+        <v>516156</v>
       </c>
       <c r="R4" t="n">
-        <v>6348485</v>
+        <v>6348543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>97377</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1364,50 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>92234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R9" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,45 +1461,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>92234</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R10" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>96352</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>97377</v>
+        <v>97389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>96364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R5" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83022</v>
+        <v>83027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83024</v>
+        <v>83029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83022</v>
+        <v>83027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>97377</v>
+        <v>96257</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>96245</v>
+        <v>97389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R15" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,6 +2037,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>97390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607424</v>
+        <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>97389</v>
+        <v>96365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516156</v>
+        <v>516155</v>
       </c>
       <c r="R4" t="n">
-        <v>6348543</v>
+        <v>6348485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>96364</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,45 +1364,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B9" t="n">
-        <v>92240</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R9" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,50 +1466,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>92241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R10" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83029</v>
+        <v>83030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>97389</v>
+        <v>97390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>96365</v>
+        <v>96370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,50 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>92246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R9" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,45 +1461,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>92241</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R10" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83030</v>
+        <v>83035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>97390</v>
+        <v>97395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>97395</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607425</v>
+        <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
+        <v>97395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516155</v>
+        <v>516156</v>
       </c>
       <c r="R4" t="n">
-        <v>6348485</v>
+        <v>6348543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>96370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R5" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B14" t="n">
-        <v>96263</v>
+        <v>97395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R14" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B15" t="n">
-        <v>97395</v>
+        <v>96263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R15" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,11 +2042,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>96370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>96370</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>97395</v>
+        <v>96263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>96263</v>
+        <v>97395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R15" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,6 +2039,11 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>riklig</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2065,6 +2065,125 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129844921</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gatu, S Lemnhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516026</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6348618</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lemnhult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>96370</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>96374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R5" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,45 +1364,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B9" t="n">
-        <v>92246</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R9" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,50 +1466,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>92250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R10" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>96263</v>
+        <v>96267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>97395</v>
+        <v>97399</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>97401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B4" t="n">
-        <v>97399</v>
+        <v>8439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R4" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>96374</v>
+        <v>96376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,50 +1364,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>92252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R9" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,45 +1461,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>92250</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R10" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83035</v>
+        <v>83037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>96267</v>
+        <v>96269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>97401</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>8439</v>
+        <v>97401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R4" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>96269</v>
+        <v>96279</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>97401</v>
+        <v>97411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>97411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607424</v>
+        <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>97411</v>
+        <v>96386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516156</v>
+        <v>516155</v>
       </c>
       <c r="R4" t="n">
-        <v>6348543</v>
+        <v>6348485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>96386</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607424</v>
+        <v>129607412</v>
       </c>
       <c r="B3" t="n">
-        <v>97411</v>
+        <v>8439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516156</v>
+        <v>516186</v>
       </c>
       <c r="R3" t="n">
-        <v>6348543</v>
+        <v>6348523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607425</v>
+        <v>129607424</v>
       </c>
       <c r="B4" t="n">
-        <v>96386</v>
+        <v>97411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516155</v>
+        <v>516156</v>
       </c>
       <c r="R4" t="n">
-        <v>6348485</v>
+        <v>6348543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607412</v>
+        <v>129607425</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>96386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516186</v>
+        <v>516155</v>
       </c>
       <c r="R5" t="n">
-        <v>6348523</v>
+        <v>6348485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>129844921</v>
       </c>
       <c r="B16" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129607412</v>
+        <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>8439</v>
+        <v>97415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516186</v>
+        <v>516156</v>
       </c>
       <c r="R3" t="n">
-        <v>6348523</v>
+        <v>6348543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129607424</v>
+        <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>97411</v>
+        <v>96390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516156</v>
+        <v>516155</v>
       </c>
       <c r="R4" t="n">
-        <v>6348543</v>
+        <v>6348485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129607425</v>
+        <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>96386</v>
+        <v>8439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516155</v>
+        <v>516186</v>
       </c>
       <c r="R5" t="n">
-        <v>6348485</v>
+        <v>6348523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83035</v>
+        <v>83038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83037</v>
+        <v>83040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83035</v>
+        <v>83038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B14" t="n">
-        <v>96279</v>
+        <v>97415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R14" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,6 +1940,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1966,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B15" t="n">
-        <v>97411</v>
+        <v>96283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R15" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,11 +2042,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129607414</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129607424</v>
       </c>
       <c r="B3" t="n">
-        <v>97415</v>
+        <v>97418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129607425</v>
       </c>
       <c r="B4" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129607412</v>
       </c>
       <c r="B5" t="n">
-        <v>8439</v>
+        <v>8440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129607433</v>
       </c>
       <c r="B6" t="n">
-        <v>83038</v>
+        <v>83041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129607430</v>
       </c>
       <c r="B7" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129607417</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129607418</v>
       </c>
       <c r="B9" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129607416</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129607415</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>129607431</v>
       </c>
       <c r="B12" t="n">
-        <v>83040</v>
+        <v>83043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>129607432</v>
       </c>
       <c r="B13" t="n">
-        <v>83038</v>
+        <v>83041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129607423</v>
+        <v>129607427</v>
       </c>
       <c r="B14" t="n">
-        <v>97415</v>
+        <v>96286</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516155</v>
+        <v>516238</v>
       </c>
       <c r="R14" t="n">
-        <v>6348529</v>
+        <v>6348540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129607427</v>
+        <v>129607423</v>
       </c>
       <c r="B15" t="n">
-        <v>96283</v>
+        <v>97418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516238</v>
+        <v>516155</v>
       </c>
       <c r="R15" t="n">
-        <v>6348540</v>
+        <v>6348529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,6 +2037,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,7 +2071,7 @@
         <v>129844921</v>
       </c>
       <c r="B16" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -1364,45 +1364,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129607418</v>
+        <v>129607416</v>
       </c>
       <c r="B9" t="n">
-        <v>92258</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516112</v>
+        <v>516055</v>
       </c>
       <c r="R9" t="n">
-        <v>6348690</v>
+        <v>6348666</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,50 +1466,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129607416</v>
+        <v>129607418</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>92258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gatu, S Lemnhult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516055</v>
+        <v>516112</v>
       </c>
       <c r="R10" t="n">
-        <v>6348666</v>
+        <v>6348690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -2071,7 +2071,7 @@
         <v>129844921</v>
       </c>
       <c r="B16" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -2071,7 +2071,7 @@
         <v>129844921</v>
       </c>
       <c r="B16" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 47684-2025 artfynd.xlsx
+++ b/artfynd/A 47684-2025 artfynd.xlsx
@@ -2071,7 +2071,7 @@
         <v>129844921</v>
       </c>
       <c r="B16" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
